--- a/Testing_Data/2022_02_Festo/Results_table_FullSize.xlsx
+++ b/Testing_Data/2022_02_Festo/Results_table_FullSize.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Bipedal_Robot\Testing_Data\2022_02_Festo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Bipedal_Robot\Testing_Data\2022_02_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92B28BD-19FE-4184-9D81-200B8CF3CB1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B9F01B-EDFC-4EDC-8139-EDA4911F933D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="6" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="6" xr2:uid="{FDAF32CB-2BA8-47E2-927E-3C1E6066A0C3}"/>
   </bookViews>
   <sheets>
     <sheet name="ExtTest40mm_1" sheetId="2" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="FlxTest20mm_42cm (3)" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1013,6 +1014,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1020,7 +1022,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1683,6 +1684,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1690,7 +1692,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2293,6 +2294,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2300,7 +2302,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2894,6 +2895,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2901,7 +2903,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3507,6 +3508,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3514,7 +3516,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4114,6 +4115,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4121,7 +4123,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8044,24 +8045,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DDD6FA0-ED90-4B9F-A1DF-3E2DAEF07409}">
   <dimension ref="A1:Q34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="25.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="3"/>
+    <col min="2" max="2" width="25.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="9" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -8069,7 +8070,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -8090,7 +8091,7 @@
         <v>0.17953321364452424</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>15</v>
       </c>
@@ -8104,7 +8105,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -8154,7 +8155,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -8201,7 +8202,7 @@
         <v>19.314</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -8248,7 +8249,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -8298,7 +8299,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
       <c r="B9" s="8" t="s">
         <v>13</v>
@@ -8346,7 +8347,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>3</v>
@@ -8394,7 +8395,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="8" t="s">
         <v>32</v>
@@ -8456,7 +8457,7 @@
         <v>0.22800718132854578</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>8</v>
       </c>
@@ -8464,7 +8465,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
@@ -8515,7 +8516,7 @@
         <v>366.05</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -8563,13 +8564,13 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
@@ -8634,22 +8635,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="J17" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O18" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="O19" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>41</v>
       </c>
@@ -8657,7 +8658,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C21">
         <v>6.1297215268519301</v>
       </c>
@@ -8665,7 +8666,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C22">
         <v>2.7479725044346299</v>
       </c>
@@ -8679,7 +8680,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C23">
         <v>1.5877091527759399</v>
       </c>
@@ -8693,12 +8694,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C24">
         <v>0.39396830053809201</v>
       </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C25">
         <v>0.87997523971335201</v>
       </c>
@@ -8706,7 +8707,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C26">
         <v>1.3017605698980601</v>
       </c>
@@ -8720,7 +8721,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C27">
         <v>0.32710826122173697</v>
       </c>
@@ -8734,37 +8735,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C28">
         <v>5.7663175704745298</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C29">
         <v>0.99793195771798704</v>
       </c>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C30">
         <v>1.17473937755851</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C31">
         <v>5.6669972560913404</v>
       </c>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C32">
         <v>3.0532323371378101</v>
       </c>
     </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C33">
         <v>9.8822570388584001</v>
       </c>
     </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C34">
         <v>5.8339811315985299</v>
       </c>
@@ -8779,24 +8780,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A3F4CC-F96C-44DD-922E-2824BD5D818E}">
   <dimension ref="A1:Q27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="25.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="3"/>
+    <col min="2" max="2" width="25.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="9" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -8804,7 +8805,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -8813,7 +8814,7 @@
         <v>462.31</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>15</v>
       </c>
@@ -8821,7 +8822,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -8871,7 +8872,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -8882,7 +8883,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -8893,7 +8894,7 @@
         <v>-16</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>33</v>
       </c>
@@ -8904,7 +8905,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -8915,7 +8916,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>13</v>
@@ -8966,7 +8967,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="8" t="s">
         <v>3</v>
@@ -8975,7 +8976,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="12"/>
       <c r="B12" s="8" t="s">
         <v>34</v>
@@ -8985,7 +8986,7 @@
         <v>0.28366247755834828</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>8</v>
       </c>
@@ -8993,7 +8994,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>10</v>
@@ -9044,7 +9045,7 @@
         <v>240.61</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="12"/>
       <c r="B15" s="8" t="s">
         <v>11</v>
@@ -9053,13 +9054,13 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
         <v>6</v>
       </c>
@@ -9124,7 +9125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
         <v>27</v>
       </c>
@@ -9135,12 +9136,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
         <v>28</v>
       </c>
@@ -9151,7 +9152,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
         <v>29</v>
       </c>
@@ -9169,7 +9170,7 @@
         <v>18.260899999999999</v>
       </c>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C23">
         <v>2.018E-2</v>
       </c>
@@ -9180,12 +9181,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
         <v>29</v>
       </c>
@@ -9199,7 +9200,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C27">
         <v>3.619E-2</v>
       </c>
@@ -9219,24 +9220,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55F358BD-411F-4156-AA93-0DF96BD5C242}">
   <dimension ref="A1:X21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="25.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="3"/>
+    <col min="2" max="2" width="25.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="9" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -9244,7 +9245,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -9267,7 +9268,7 @@
         <v>0.12647754137115841</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
@@ -9284,7 +9285,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -9340,7 +9341,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -9396,7 +9397,7 @@
         <v>4.8666</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -9452,7 +9453,7 @@
         <v>-120</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
         <v>37</v>
       </c>
@@ -9508,7 +9509,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -9567,7 +9568,7 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>13</v>
@@ -9624,7 +9625,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="8" t="s">
         <v>3</v>
@@ -9686,7 +9687,7 @@
       <c r="W11"/>
       <c r="X11"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>8</v>
       </c>
@@ -9709,7 +9710,7 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
@@ -9766,7 +9767,7 @@
         <v>366.43</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -9823,13 +9824,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
@@ -9902,7 +9903,7 @@
         <v>-1.0937153129886135</v>
       </c>
     </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>42</v>
       </c>
@@ -9958,22 +9959,22 @@
         <v>-0.77272430551831095</v>
       </c>
     </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:19" x14ac:dyDescent="0.25">
       <c r="J18" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
       <c r="M19" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
       <c r="R20" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>41</v>
       </c>
@@ -9991,24 +9992,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA058C6-A5F1-41EF-81BC-5D2D9F894F5C}">
   <dimension ref="A1:X21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="25.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="3"/>
+    <col min="2" max="2" width="25.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="9" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -10023,7 +10024,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -10053,7 +10054,7 @@
         <v>0.12647754137115841</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
@@ -10073,7 +10074,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -10129,7 +10130,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -10155,7 +10156,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -10181,7 +10182,7 @@
         <v>-64</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
         <v>37</v>
       </c>
@@ -10207,7 +10208,7 @@
         <v>606.5</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -10215,7 +10216,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>13</v>
@@ -10242,7 +10243,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="8" t="s">
         <v>3</v>
@@ -10282,7 +10283,7 @@
       <c r="W11"/>
       <c r="X11"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>8</v>
       </c>
@@ -10305,7 +10306,7 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
@@ -10359,7 +10360,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -10383,13 +10384,13 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
@@ -10462,12 +10463,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>41</v>
       </c>
@@ -10485,24 +10486,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2201CA6F-EFE7-4253-8041-7C38B87FE418}">
   <dimension ref="A1:X21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="25.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="3"/>
+    <col min="2" max="2" width="25.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="9" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -10517,7 +10518,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -10547,7 +10548,7 @@
         <v>0.12647754137115841</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
@@ -10561,7 +10562,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -10617,7 +10618,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -10634,7 +10635,7 @@
         <v>50.45</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -10651,7 +10652,7 @@
         <v>-75</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
         <v>37</v>
       </c>
@@ -10668,7 +10669,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -10676,7 +10677,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>13</v>
@@ -10694,7 +10695,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="8" t="s">
         <v>3</v>
@@ -10730,7 +10731,7 @@
       <c r="W11"/>
       <c r="X11"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>8</v>
       </c>
@@ -10753,7 +10754,7 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
@@ -10807,7 +10808,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -10825,13 +10826,13 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
@@ -10904,7 +10905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>42</v>
       </c>
@@ -10912,7 +10913,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>41</v>
       </c>
@@ -10930,24 +10931,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE3C0B61-7108-442E-B33C-1C6DD21F395D}">
   <dimension ref="A1:X21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="25.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="3"/>
+    <col min="2" max="2" width="25.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="9" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -10962,7 +10963,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -10983,7 +10984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
@@ -10994,7 +10995,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -11050,7 +11051,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
@@ -11079,7 +11080,7 @@
         <v>78.14</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -11108,7 +11109,7 @@
         <v>-32</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
         <v>37</v>
       </c>
@@ -11137,7 +11138,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>7</v>
       </c>
@@ -11145,7 +11146,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="8" t="s">
         <v>13</v>
@@ -11175,7 +11176,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="8" t="s">
         <v>3</v>
@@ -11219,7 +11220,7 @@
       <c r="W11"/>
       <c r="X11"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>8</v>
       </c>
@@ -11242,7 +11243,7 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
       <c r="B13" s="8" t="s">
         <v>10</v>
@@ -11296,7 +11297,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="8" t="s">
         <v>11</v>
@@ -11326,13 +11327,13 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
@@ -11405,7 +11406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>42</v>
       </c>
@@ -11428,7 +11429,7 @@
         <v>-22.190799999999999</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>41</v>
       </c>
@@ -11446,24 +11447,24 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1B5784E-5F9E-4AE8-9F2F-3ECBE91B1B37}">
   <dimension ref="A1:AD21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="3"/>
-    <col min="2" max="2" width="25.109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="9" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="3"/>
+    <col min="2" max="2" width="25.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="9" width="13.42578125" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -11478,7 +11479,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -11504,7 +11505,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
@@ -11524,7 +11525,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:30" s="27" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:30" s="27" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="23"/>
       <c r="B5" s="24" t="s">
         <v>0</v>
@@ -11614,7 +11615,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B6" s="13" t="s">
         <v>1</v>
       </c>
@@ -11685,7 +11686,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
         <v>2</v>
       </c>
@@ -11756,7 +11757,7 @@
         <v>-32</v>
       </c>
     </row>
-    <row r="8" spans="1:30" s="32" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:30" s="32" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="28"/>
       <c r="B8" s="29" t="s">
         <v>37</v>
@@ -11828,7 +11829,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>7</v>
       </c>
@@ -11858,7 +11859,7 @@
       <c r="W9" s="21"/>
       <c r="X9" s="21"/>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="3" t="s">
         <v>13</v>
@@ -11930,7 +11931,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="11" spans="1:30" s="34" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:30" s="34" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="33"/>
       <c r="B11" s="28" t="s">
         <v>3</v>
@@ -12002,7 +12003,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>8</v>
       </c>
@@ -12032,7 +12033,7 @@
       <c r="W12" s="21"/>
       <c r="X12" s="21"/>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
       <c r="B13" s="3" t="s">
         <v>10</v>
@@ -12122,7 +12123,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="3" t="s">
         <v>11</v>
@@ -12194,7 +12195,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:30" s="32" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:30" s="32" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="33"/>
       <c r="B15" s="28" t="s">
         <v>4</v>
@@ -12222,7 +12223,7 @@
       <c r="W15" s="30"/>
       <c r="X15" s="30"/>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B16" s="13" t="s">
         <v>6</v>
       </c>
@@ -12339,7 +12340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>42</v>
       </c>
@@ -12410,7 +12411,7 @@
         <v>-23.6068</v>
       </c>
     </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:24" x14ac:dyDescent="0.25">
       <c r="K18" t="s">
         <v>47</v>
       </c>
@@ -12418,7 +12419,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:24" x14ac:dyDescent="0.25">
       <c r="U19" t="s">
         <v>49</v>
       </c>
@@ -12426,7 +12427,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:24" x14ac:dyDescent="0.25">
       <c r="F20" t="s">
         <v>53</v>
       </c>
@@ -12434,7 +12435,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>41</v>
       </c>
